--- a/artfynd/A 22469-2024 artfynd.xlsx
+++ b/artfynd/A 22469-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110242013</v>
+        <v>110242018</v>
       </c>
       <c r="B2" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229748</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547155.9314794622</v>
+        <v>547136</v>
       </c>
       <c r="R2" t="n">
-        <v>7012401.618361745</v>
+        <v>7012163</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110242016</v>
+        <v>110242017</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547171.4239177565</v>
+        <v>547173</v>
       </c>
       <c r="R3" t="n">
-        <v>7012360.825342371</v>
+        <v>7012362</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110242017</v>
+        <v>110242016</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547173.2026898284</v>
+        <v>547172</v>
       </c>
       <c r="R4" t="n">
-        <v>7012362.654446226</v>
+        <v>7012361</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +981,7 @@
         <v>110242015</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547155.9314794622</v>
+        <v>547156</v>
       </c>
       <c r="R5" t="n">
-        <v>7012401.618361745</v>
+        <v>7012401</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,12 +1082,7 @@
         <v>110242012</v>
       </c>
       <c r="B6" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>547100.5742802671</v>
+        <v>547101</v>
       </c>
       <c r="R6" t="n">
-        <v>7012266.929720426</v>
+        <v>7012267</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,6 +1173,107 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110242013</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bäckmanstorpet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>547156</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7012401</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 22469-2024 artfynd.xlsx
+++ b/artfynd/A 22469-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110242018</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110242017</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110242016</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110242015</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110242012</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110242013</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>